--- a/margin_repository/Reconciliation_Report.xlsx
+++ b/margin_repository/Reconciliation_Report.xlsx
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Batch: B20260731225129-14933e</t>
+          <t>Batch: B20260731230447-b6add7</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
